--- a/06_plan/prosjektplan_msproject.xlsx
+++ b/06_plan/prosjektplan_msproject.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$I$15</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,16 +30,40 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -51,14 +77,49 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9E2F3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9E2F3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9E2F3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9E2F3"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -425,387 +486,699 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="62" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Task Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Start Date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Finish Date</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Duration (Days)</t>
         </is>
       </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Realistisk start</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Realistisk slutt</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Kommentar</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Prosjektoppstart &amp; Plan</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>2026-02-15</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>2026-03-09</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="4" t="n">
         <v>22</v>
       </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>Ferdig</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>Gjennomført som planlagt.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Milepæl M1: Godkjent beskrivelse</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>2026-03-09</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>2026-03-09</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>Milestone</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Ferdig</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>Prosjektbeskrivelse godkjent.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Innhenting av trafikkdata (Avinor)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>2026-03-09</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="4" t="n">
         <v>22</v>
       </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Ferdig</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Datatilgang og avklaringer tok noe lenger tid enn opprinnelig plan.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Strukturering av datagrunnlag</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>2026-04-05</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="4" t="n">
         <v>16</v>
       </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Ferdig</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Gjennomført med datavask og klargjøring for simulering.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Milepæl M2: Datagrunnlag etablert</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Milestone</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Ferdig</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>Ferdigstilt etter kobling av ankomst- og avgangsrotasjoner.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Konseptuell modellering</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="4" t="n">
         <v>29</v>
       </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Ferdig</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>Modellstruktur og ressurslogikk avklart.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Milepæl M3: Konseptuell modell ferdig</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Milestone</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Ferdig</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Konseptuell modell ferdigstilt.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Programmering (Python/SimPy)</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="4" t="n">
         <v>14</v>
       </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Ferdig</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>Implementering, feilsøking og verifisering overlappet i praksis.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Milepæl M4: Simuleringsmodell ferdig</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>Milestone</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Ferdig</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>Kjørbar modell med baseline og scenariooppsett.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Baseline-analyse &amp; Testing</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="4" t="n">
         <v>6</v>
       </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Ferdig</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>Baseline kjørt og plausibilitetssjekket.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Scenarioanalyse</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="4" t="n">
         <v>6</v>
       </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Ferdig</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>Scenarioer kjørt på nytt med 5 min venteterskel.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Sluttføring av rapport</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="4" t="n">
         <v>11</v>
       </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Pågår</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>Resultater og diskusjon oppdatert; siste språkvask og konsistenskontroll gjenstår.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Innlevering</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Ikke startet</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Planlagt innleveringsdag.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Milepæl M5: Endelig innlevering</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Milestone</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>Ikke startet</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Endelig frist.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>